--- a/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260730.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00713/ETF_Investment_Portfolio_20260730.xlsx
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2458</t>
+          <t>9917</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>義隆</t>
+          <t>中保科</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>8,032,000</t>
+          <t>10,742,000</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1173,17 +1173,17 @@
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>9917</t>
+          <t>2458</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>中保科</t>
+          <t>義隆</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>10,742,000</t>
+          <t>8,032,000</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
